--- a/STOK RANK/Current non current.xlsx
+++ b/STOK RANK/Current non current.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\prototipe cek stok\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\DASHBOARD RANK STOK\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7D0C0E-E368-43E1-B91E-B0F79D194A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789751DF-08AC-433C-A331-B050ABE932E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,12 +23,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12967" uniqueCount="4436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13324" uniqueCount="4547">
   <si>
     <t>Material</t>
   </si>
@@ -13213,48 +13224,6 @@
     <t>ONEHEART PHONESTAND TUMBLER</t>
   </si>
   <si>
-    <t>ACCEC 3</t>
-  </si>
-  <si>
-    <t>ACCEC 4</t>
-  </si>
-  <si>
-    <t>ACCEC 5</t>
-  </si>
-  <si>
-    <t>ACCEC 6</t>
-  </si>
-  <si>
-    <t>ACCEC 7</t>
-  </si>
-  <si>
-    <t>ACCEC 8</t>
-  </si>
-  <si>
-    <t>ACCEC 9</t>
-  </si>
-  <si>
-    <t>ACCEC 10</t>
-  </si>
-  <si>
-    <t>ACCEC 11</t>
-  </si>
-  <si>
-    <t>ACCEC 12</t>
-  </si>
-  <si>
-    <t>ACCEC 13</t>
-  </si>
-  <si>
-    <t>ACCEC 14</t>
-  </si>
-  <si>
-    <t>ACCEC 15</t>
-  </si>
-  <si>
-    <t>ACCEC 16</t>
-  </si>
-  <si>
     <t>CLASSIC DNM SHIRT BLACK S</t>
   </si>
   <si>
@@ -13318,31 +13287,406 @@
     <t>CLASSIC DNM SHIRT GREY S</t>
   </si>
   <si>
-    <t>AHK00001017</t>
-  </si>
-  <si>
     <t>CLASSIC DNM SHIRT GREY M</t>
   </si>
   <si>
-    <t>AHK01001017</t>
-  </si>
-  <si>
     <t>CLASSIC DNM SHIRT GREY L</t>
   </si>
   <si>
-    <t>AHK02001017</t>
-  </si>
-  <si>
     <t>CLASSIC DNM SHIRT GREY XL</t>
   </si>
   <si>
-    <t>AHK03001017</t>
-  </si>
-  <si>
     <t>CLASSIC DNM SHIRT GREY XXL</t>
   </si>
   <si>
-    <t>AHK04001017</t>
+    <t>AHK00003017</t>
+  </si>
+  <si>
+    <t>AHK01003017</t>
+  </si>
+  <si>
+    <t>AHK02003017</t>
+  </si>
+  <si>
+    <t>AHK03003017</t>
+  </si>
+  <si>
+    <t>AHK04003017</t>
+  </si>
+  <si>
+    <t>86100H04MA0</t>
+  </si>
+  <si>
+    <t>HELMET ASSY HALF FACE TYPE 1</t>
+  </si>
+  <si>
+    <t>AHJK0101AS8</t>
+  </si>
+  <si>
+    <t>MM93 LOS. AIR JACKET RED M</t>
+  </si>
+  <si>
+    <t>AHJK0401AS9</t>
+  </si>
+  <si>
+    <t>MM93 SPG WP JACKET BRW XXL</t>
+  </si>
+  <si>
+    <t>0800AK1AL00</t>
+  </si>
+  <si>
+    <t>ACC KIT A ALL BEAT 24</t>
+  </si>
+  <si>
+    <t>0800CK1AL00</t>
+  </si>
+  <si>
+    <t>ACC KIT C ALL BEAT 24</t>
+  </si>
+  <si>
+    <t>86100H05PA0</t>
+  </si>
+  <si>
+    <t>HELMET ASSY RETRO STYLO</t>
+  </si>
+  <si>
+    <t>AHIP0001001</t>
+  </si>
+  <si>
+    <t>IRON ON PATCH QUOTES VER.</t>
+  </si>
+  <si>
+    <t>AHIP0001002</t>
+  </si>
+  <si>
+    <t>IRON ON PATCH BIKE VER.</t>
+  </si>
+  <si>
+    <t>08T80K0WW00</t>
+  </si>
+  <si>
+    <t>Center Pad</t>
+  </si>
+  <si>
+    <t>08R74K0WW00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air Scoop </t>
+  </si>
+  <si>
+    <t>08F47K0WW00</t>
+  </si>
+  <si>
+    <t>Rear Pad</t>
+  </si>
+  <si>
+    <t>64300K0WW00</t>
+  </si>
+  <si>
+    <t>Panel Step Floor</t>
+  </si>
+  <si>
+    <t>64301K0WW00</t>
+  </si>
+  <si>
+    <t>Garnish Front</t>
+  </si>
+  <si>
+    <t>8350BK0WW00</t>
+  </si>
+  <si>
+    <t>Side Pad Rubber</t>
+  </si>
+  <si>
+    <t>AHJK0001034</t>
+  </si>
+  <si>
+    <t>BLOUSON JACKET BLACK  (S)</t>
+  </si>
+  <si>
+    <t>AHJK0101034</t>
+  </si>
+  <si>
+    <t>BLOUSON JACKET BLACK   (M)</t>
+  </si>
+  <si>
+    <t>AHJK0201034</t>
+  </si>
+  <si>
+    <t>BLOUSON JACKET BLACK   (L)</t>
+  </si>
+  <si>
+    <t>AHJK0301034</t>
+  </si>
+  <si>
+    <t>BLOUSON JACKET BLACK   (XL)</t>
+  </si>
+  <si>
+    <t>AHJK0401034</t>
+  </si>
+  <si>
+    <t>BLOUSON JACKET BLACK   (XXL)</t>
+  </si>
+  <si>
+    <t>AHRC0101001</t>
+  </si>
+  <si>
+    <t>RAINCOAT SET BLACK (M)</t>
+  </si>
+  <si>
+    <t>AHRC0201001</t>
+  </si>
+  <si>
+    <t>RAINCOAT SET BLACK  (L)</t>
+  </si>
+  <si>
+    <t>AHRC0301001</t>
+  </si>
+  <si>
+    <t>RAINCOAT SET BLACK  (XL)</t>
+  </si>
+  <si>
+    <t>AHGL0001016</t>
+  </si>
+  <si>
+    <t>MIX MATERIAL GLOVES BLACK (M)</t>
+  </si>
+  <si>
+    <t>AHGL0101016</t>
+  </si>
+  <si>
+    <t>MIX MATERIAL GLOVES BLACK (L)</t>
+  </si>
+  <si>
+    <t>AHGL0201016</t>
+  </si>
+  <si>
+    <t>MIX MATERIAL GLOVES BLACK (XL)</t>
+  </si>
+  <si>
+    <t>AHTA0001013</t>
+  </si>
+  <si>
+    <t>TRAVEL BACKPACK BLACK</t>
+  </si>
+  <si>
+    <t>91600K2FY00</t>
+  </si>
+  <si>
+    <t>REAR RACK SCOOPY</t>
+  </si>
+  <si>
+    <t>Scoopy</t>
+  </si>
+  <si>
+    <t>08S10K2FY00</t>
+  </si>
+  <si>
+    <t>WIND SCREEN SCOOPY</t>
+  </si>
+  <si>
+    <t>871X0K2FYRE</t>
+  </si>
+  <si>
+    <t>STICKER SET RED SCOOPY</t>
+  </si>
+  <si>
+    <t>871X0K2FYBL</t>
+  </si>
+  <si>
+    <t>STICKER SET BLACK SCOOPY</t>
+  </si>
+  <si>
+    <t>871X0K2FYMI</t>
+  </si>
+  <si>
+    <t>STICKER SET MINT SCOOPY</t>
+  </si>
+  <si>
+    <t>871X0K2FYCR</t>
+  </si>
+  <si>
+    <t>STICKER SET CREAM SCOOPY</t>
+  </si>
+  <si>
+    <t>772A0K0JJ00</t>
+  </si>
+  <si>
+    <t>SEAT COVER GENIO</t>
+  </si>
+  <si>
+    <t>08F88K0JJYL</t>
+  </si>
+  <si>
+    <t>GARNISH MUFFLER GENIO YLW</t>
+  </si>
+  <si>
+    <t>08F88K0JJWH</t>
+  </si>
+  <si>
+    <t>GARNISH MUFFLER GENIO WHT</t>
+  </si>
+  <si>
+    <t>61304K0JJYL</t>
+  </si>
+  <si>
+    <t>GARN PANEL MTR GENIO YLW</t>
+  </si>
+  <si>
+    <t>61304K0JJWH</t>
+  </si>
+  <si>
+    <t>GARN PANEL MTR GENIO WHT</t>
+  </si>
+  <si>
+    <t>08F44K0JJYL</t>
+  </si>
+  <si>
+    <t>GARN FAN COVER GENIO YLW</t>
+  </si>
+  <si>
+    <t>08F44K0JJWH</t>
+  </si>
+  <si>
+    <t>GARN FAN COVER GENIO WHT</t>
+  </si>
+  <si>
+    <t>17200K0JJYL</t>
+  </si>
+  <si>
+    <t>GRN AIR CLEANER GENIO YLW</t>
+  </si>
+  <si>
+    <t>17200K0JJWH</t>
+  </si>
+  <si>
+    <t>GRN AIR CLEANER GENIO WHT</t>
+  </si>
+  <si>
+    <t>AHGK0010018</t>
+  </si>
+  <si>
+    <t>HRC25 BWG ID CARD HOLDER</t>
+  </si>
+  <si>
+    <t>AHK00003018</t>
+  </si>
+  <si>
+    <t>HRC25 NAVY BLUE SHIRT S</t>
+  </si>
+  <si>
+    <t>AHK01003018</t>
+  </si>
+  <si>
+    <t>HRC25 NAVY BLUE SHIRT M</t>
+  </si>
+  <si>
+    <t>AHK02003018</t>
+  </si>
+  <si>
+    <t>HRC25 NAVY BLUE SHIRT L</t>
+  </si>
+  <si>
+    <t>AHK03003018</t>
+  </si>
+  <si>
+    <t>HRC25 NAVY BLUE SHIRT XL</t>
+  </si>
+  <si>
+    <t>AHK04003018</t>
+  </si>
+  <si>
+    <t>HRC25 NAVY BLUE SHIRT XXL</t>
+  </si>
+  <si>
+    <t>AHPS0001014</t>
+  </si>
+  <si>
+    <t>HRC25 BWG DRYFIT POLO S</t>
+  </si>
+  <si>
+    <t>AHPS0101014</t>
+  </si>
+  <si>
+    <t>HRC25 BWG DRYFIT POLO M</t>
+  </si>
+  <si>
+    <t>AHPS0201014</t>
+  </si>
+  <si>
+    <t>HRC25 BWG DRYFIT POLO L</t>
+  </si>
+  <si>
+    <t>AHPS0301014</t>
+  </si>
+  <si>
+    <t>HRC25 BWG DRYFIT POLO XL</t>
+  </si>
+  <si>
+    <t>AHPS0401014</t>
+  </si>
+  <si>
+    <t>HRC25 BWG DRYFIT POLO XXL</t>
+  </si>
+  <si>
+    <t>AHTA0001012</t>
+  </si>
+  <si>
+    <t>HRC25 BWG SLING BAG</t>
+  </si>
+  <si>
+    <t>AHTP0001019</t>
+  </si>
+  <si>
+    <t>HRC25 BWG CAP</t>
+  </si>
+  <si>
+    <t>AHTS0001057</t>
+  </si>
+  <si>
+    <t>HRC25 BWG DRYFIT TSHIRT S</t>
+  </si>
+  <si>
+    <t>AHTS0101057</t>
+  </si>
+  <si>
+    <t>HRC25 BWG DRYFIT TSHIRT M</t>
+  </si>
+  <si>
+    <t>AHTS0201057</t>
+  </si>
+  <si>
+    <t>HRC25 BWG DRYFIT TSHIRT L</t>
+  </si>
+  <si>
+    <t>AHTS0301057</t>
+  </si>
+  <si>
+    <t>HRC25 BWG DRYFIT TSHIRT XL</t>
+  </si>
+  <si>
+    <t>AHTS0401057</t>
+  </si>
+  <si>
+    <t>HRC25 BWG DRYFIT TSHIRT XXL</t>
+  </si>
+  <si>
+    <t>AHUB0001002</t>
+  </si>
+  <si>
+    <t>HRC25 BWG TRAVEL UMBRELLA</t>
+  </si>
+  <si>
+    <t>MCSMPK0WW00</t>
+  </si>
+  <si>
+    <t>SPDMTR PRTECTOR ADV 160 RS</t>
+  </si>
+  <si>
+    <t>MCSMPK0WWCA</t>
+  </si>
+  <si>
+    <t>SPDMTR PRTECTOR ADV 160 C/A</t>
   </si>
 </sst>
 </file>
@@ -13565,7 +13909,67 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -13902,7 +14306,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2161"/>
+  <dimension ref="A1:J2224"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="3" bestFit="1" customWidth="1"/>
@@ -22877,7 +23281,7 @@
         <v>9</v>
       </c>
       <c r="D374" s="4">
-        <v>307100</v>
+        <v>310800</v>
       </c>
       <c r="E374" s="2" t="s">
         <v>152</v>
@@ -35357,7 +35761,7 @@
         <v>1785</v>
       </c>
       <c r="D894" s="4">
-        <v>59340</v>
+        <v>60030</v>
       </c>
       <c r="E894" s="2" t="s">
         <v>1786</v>
@@ -35381,7 +35785,7 @@
         <v>1785</v>
       </c>
       <c r="D895" s="4">
-        <v>89010</v>
+        <v>89700</v>
       </c>
       <c r="E895" s="2" t="s">
         <v>1786</v>
@@ -35429,7 +35833,7 @@
         <v>1785</v>
       </c>
       <c r="D897" s="4">
-        <v>414000</v>
+        <v>417450</v>
       </c>
       <c r="E897" s="2" t="s">
         <v>1786</v>
@@ -35453,7 +35857,7 @@
         <v>1785</v>
       </c>
       <c r="D898" s="4">
-        <v>33810</v>
+        <v>34155</v>
       </c>
       <c r="E898" s="2" t="s">
         <v>1786</v>
@@ -35477,7 +35881,7 @@
         <v>1785</v>
       </c>
       <c r="D899" s="4">
-        <v>59340</v>
+        <v>60030</v>
       </c>
       <c r="E899" s="2" t="s">
         <v>3738</v>
@@ -35501,7 +35905,7 @@
         <v>1785</v>
       </c>
       <c r="D900" s="4">
-        <v>59340</v>
+        <v>60030</v>
       </c>
       <c r="E900" s="2" t="s">
         <v>3738</v>
@@ -35525,7 +35929,7 @@
         <v>1785</v>
       </c>
       <c r="D901" s="4">
-        <v>112125</v>
+        <v>113160</v>
       </c>
       <c r="E901" s="2" t="s">
         <v>1808</v>
@@ -35549,7 +35953,7 @@
         <v>1785</v>
       </c>
       <c r="D902" s="4">
-        <v>59340</v>
+        <v>60030</v>
       </c>
       <c r="E902" s="2" t="s">
         <v>3738</v>
@@ -35597,7 +36001,7 @@
         <v>1785</v>
       </c>
       <c r="D904" s="4">
-        <v>146970</v>
+        <v>148350</v>
       </c>
       <c r="E904" s="2" t="s">
         <v>1808</v>
@@ -35621,7 +36025,7 @@
         <v>1785</v>
       </c>
       <c r="D905" s="4">
-        <v>111090</v>
+        <v>112125</v>
       </c>
       <c r="E905" s="2" t="s">
         <v>1808</v>
@@ -35645,7 +36049,7 @@
         <v>1785</v>
       </c>
       <c r="D906" s="4">
-        <v>114540</v>
+        <v>115575</v>
       </c>
       <c r="E906" s="2" t="s">
         <v>1808</v>
@@ -35693,7 +36097,7 @@
         <v>1785</v>
       </c>
       <c r="D908" s="4">
-        <v>73830</v>
+        <v>74520</v>
       </c>
       <c r="E908" s="2" t="s">
         <v>1827</v>
@@ -35717,7 +36121,7 @@
         <v>1785</v>
       </c>
       <c r="D909" s="4">
-        <v>105225</v>
+        <v>106260</v>
       </c>
       <c r="E909" s="2" t="s">
         <v>1833</v>
@@ -35741,7 +36145,7 @@
         <v>1785</v>
       </c>
       <c r="D910" s="4">
-        <v>105225</v>
+        <v>106260</v>
       </c>
       <c r="E910" s="2" t="s">
         <v>1833</v>
@@ -35765,7 +36169,7 @@
         <v>1785</v>
       </c>
       <c r="D911" s="4">
-        <v>77280</v>
+        <v>77970</v>
       </c>
       <c r="E911" s="2" t="s">
         <v>1833</v>
@@ -35789,7 +36193,7 @@
         <v>1785</v>
       </c>
       <c r="D912" s="4">
-        <v>87630</v>
+        <v>88320</v>
       </c>
       <c r="E912" s="2" t="s">
         <v>1833</v>
@@ -35837,7 +36241,7 @@
         <v>1785</v>
       </c>
       <c r="D914" s="4">
-        <v>37260</v>
+        <v>37605</v>
       </c>
       <c r="E914" s="2" t="s">
         <v>3719</v>
@@ -35861,7 +36265,7 @@
         <v>1785</v>
       </c>
       <c r="D915" s="4">
-        <v>81420</v>
+        <v>82110</v>
       </c>
       <c r="E915" s="2" t="s">
         <v>3719</v>
@@ -35885,7 +36289,7 @@
         <v>1785</v>
       </c>
       <c r="D916" s="4">
-        <v>81420</v>
+        <v>82110</v>
       </c>
       <c r="E916" s="2" t="s">
         <v>631</v>
@@ -35909,7 +36313,7 @@
         <v>1785</v>
       </c>
       <c r="D917" s="4">
-        <v>73830</v>
+        <v>74520</v>
       </c>
       <c r="E917" s="2" t="s">
         <v>631</v>
@@ -36005,7 +36409,7 @@
         <v>1785</v>
       </c>
       <c r="D921" s="4">
-        <v>35190</v>
+        <v>35535</v>
       </c>
       <c r="E921" s="2" t="s">
         <v>1863</v>
@@ -36029,7 +36433,7 @@
         <v>1785</v>
       </c>
       <c r="D922" s="4">
-        <v>84180</v>
+        <v>84870</v>
       </c>
       <c r="E922" s="2" t="s">
         <v>1863</v>
@@ -36077,7 +36481,7 @@
         <v>1785</v>
       </c>
       <c r="D924" s="4">
-        <v>105225</v>
+        <v>106260</v>
       </c>
       <c r="E924" s="2" t="s">
         <v>631</v>
@@ -36293,7 +36697,7 @@
         <v>1785</v>
       </c>
       <c r="D933" s="4">
-        <v>111090</v>
+        <v>112125</v>
       </c>
       <c r="E933" s="2" t="s">
         <v>1894</v>
@@ -36317,7 +36721,7 @@
         <v>1785</v>
       </c>
       <c r="D934" s="4">
-        <v>140070</v>
+        <v>141450</v>
       </c>
       <c r="E934" s="2" t="s">
         <v>1894</v>
@@ -36797,7 +37201,7 @@
         <v>1785</v>
       </c>
       <c r="D954" s="4">
-        <v>73830</v>
+        <v>74520</v>
       </c>
       <c r="E954" s="2" t="s">
         <v>1937</v>
@@ -36821,7 +37225,7 @@
         <v>1785</v>
       </c>
       <c r="D955" s="4">
-        <v>99360</v>
+        <v>100395</v>
       </c>
       <c r="E955" s="2" t="s">
         <v>1937</v>
@@ -36893,7 +37297,7 @@
         <v>1785</v>
       </c>
       <c r="D958" s="4">
-        <v>143520</v>
+        <v>144900</v>
       </c>
       <c r="E958" s="2" t="s">
         <v>1937</v>
@@ -36917,7 +37321,7 @@
         <v>1785</v>
       </c>
       <c r="D959" s="4">
-        <v>143520</v>
+        <v>144900</v>
       </c>
       <c r="E959" s="2" t="s">
         <v>1937</v>
@@ -36941,7 +37345,7 @@
         <v>1785</v>
       </c>
       <c r="D960" s="4">
-        <v>111090</v>
+        <v>112125</v>
       </c>
       <c r="E960" s="2" t="s">
         <v>1937</v>
@@ -36950,7 +37354,7 @@
         <v>1824</v>
       </c>
       <c r="G960" s="2" t="s">
-        <v>324</v>
+        <v>11</v>
       </c>
       <c r="J960" s="24"/>
     </row>
@@ -36965,7 +37369,7 @@
         <v>1785</v>
       </c>
       <c r="D961" s="4">
-        <v>111090</v>
+        <v>112125</v>
       </c>
       <c r="E961" s="2" t="s">
         <v>1937</v>
@@ -36974,7 +37378,7 @@
         <v>1824</v>
       </c>
       <c r="G961" s="2" t="s">
-        <v>324</v>
+        <v>11</v>
       </c>
       <c r="J961" s="24"/>
     </row>
@@ -37013,7 +37417,7 @@
         <v>1785</v>
       </c>
       <c r="D963" s="4">
-        <v>33120</v>
+        <v>33465</v>
       </c>
       <c r="E963" s="2" t="s">
         <v>1937</v>
@@ -37037,7 +37441,7 @@
         <v>1785</v>
       </c>
       <c r="D964" s="4">
-        <v>33120</v>
+        <v>33465</v>
       </c>
       <c r="E964" s="2" t="s">
         <v>1937</v>
@@ -37061,7 +37465,7 @@
         <v>1785</v>
       </c>
       <c r="D965" s="4">
-        <v>33120</v>
+        <v>33465</v>
       </c>
       <c r="E965" s="2" t="s">
         <v>1937</v>
@@ -37085,7 +37489,7 @@
         <v>1785</v>
       </c>
       <c r="D966" s="4">
-        <v>33120</v>
+        <v>33465</v>
       </c>
       <c r="E966" s="2" t="s">
         <v>1937</v>
@@ -37349,7 +37753,7 @@
         <v>1785</v>
       </c>
       <c r="D977" s="4">
-        <v>62790</v>
+        <v>63480</v>
       </c>
       <c r="E977" s="2" t="s">
         <v>1994</v>
@@ -37397,7 +37801,7 @@
         <v>1785</v>
       </c>
       <c r="D979" s="4">
-        <v>116610</v>
+        <v>117990</v>
       </c>
       <c r="E979" s="2" t="s">
         <v>1994</v>
@@ -37421,7 +37825,7 @@
         <v>1785</v>
       </c>
       <c r="D980" s="4">
-        <v>64860</v>
+        <v>65550</v>
       </c>
       <c r="E980" s="2" t="s">
         <v>1994</v>
@@ -37469,7 +37873,7 @@
         <v>1785</v>
       </c>
       <c r="D982" s="4">
-        <v>93495</v>
+        <v>94530</v>
       </c>
       <c r="E982" s="2" t="s">
         <v>1994</v>
@@ -37493,7 +37897,7 @@
         <v>1785</v>
       </c>
       <c r="D983" s="4">
-        <v>216660</v>
+        <v>218730</v>
       </c>
       <c r="E983" s="2" t="s">
         <v>1994</v>
@@ -37517,7 +37921,7 @@
         <v>1785</v>
       </c>
       <c r="D984" s="4">
-        <v>124200</v>
+        <v>125580</v>
       </c>
       <c r="E984" s="2" t="s">
         <v>1994</v>
@@ -37541,7 +37945,7 @@
         <v>1785</v>
       </c>
       <c r="D985" s="4">
-        <v>124200</v>
+        <v>125580</v>
       </c>
       <c r="E985" s="2" t="s">
         <v>1994</v>
@@ -37661,7 +38065,7 @@
         <v>1785</v>
       </c>
       <c r="D990" s="4">
-        <v>85560</v>
+        <v>86250</v>
       </c>
       <c r="E990" s="2" t="s">
         <v>3827</v>
@@ -37685,7 +38089,7 @@
         <v>1785</v>
       </c>
       <c r="D991" s="4">
-        <v>103500</v>
+        <v>104190</v>
       </c>
       <c r="E991" s="2" t="s">
         <v>3827</v>
@@ -37709,7 +38113,7 @@
         <v>1785</v>
       </c>
       <c r="D992" s="4">
-        <v>143520</v>
+        <v>144900</v>
       </c>
       <c r="E992" s="2" t="s">
         <v>3827</v>
@@ -37733,7 +38137,7 @@
         <v>1785</v>
       </c>
       <c r="D993" s="4">
-        <v>46920</v>
+        <v>47265</v>
       </c>
       <c r="E993" s="2" t="s">
         <v>3827</v>
@@ -37757,7 +38161,7 @@
         <v>1785</v>
       </c>
       <c r="D994" s="4">
-        <v>81420</v>
+        <v>82110</v>
       </c>
       <c r="E994" s="2" t="s">
         <v>3827</v>
@@ -37781,7 +38185,7 @@
         <v>1785</v>
       </c>
       <c r="D995" s="4">
-        <v>111090</v>
+        <v>112125</v>
       </c>
       <c r="E995" s="2" t="s">
         <v>3827</v>
@@ -37925,7 +38329,7 @@
         <v>1785</v>
       </c>
       <c r="D1001" s="4">
-        <v>250470</v>
+        <v>252540</v>
       </c>
       <c r="E1001" s="2" t="s">
         <v>1808</v>
@@ -37973,7 +38377,7 @@
         <v>1785</v>
       </c>
       <c r="D1003" s="4">
-        <v>220800</v>
+        <v>222870</v>
       </c>
       <c r="E1003" s="2" t="s">
         <v>1808</v>
@@ -37997,7 +38401,7 @@
         <v>1785</v>
       </c>
       <c r="D1004" s="4">
-        <v>305670</v>
+        <v>308430</v>
       </c>
       <c r="E1004" s="2" t="s">
         <v>1808</v>
@@ -38045,7 +38449,7 @@
         <v>1785</v>
       </c>
       <c r="D1006" s="4">
-        <v>305670</v>
+        <v>308430</v>
       </c>
       <c r="E1006" s="2" t="s">
         <v>1808</v>
@@ -38069,7 +38473,7 @@
         <v>1785</v>
       </c>
       <c r="D1007" s="4">
-        <v>301530</v>
+        <v>304290</v>
       </c>
       <c r="E1007" s="2" t="s">
         <v>1994</v>
@@ -38093,7 +38497,7 @@
         <v>1785</v>
       </c>
       <c r="D1008" s="4">
-        <v>489900</v>
+        <v>494040</v>
       </c>
       <c r="E1008" s="2" t="s">
         <v>1994</v>
@@ -38717,7 +39121,7 @@
         <v>1785</v>
       </c>
       <c r="D1034" s="4">
-        <v>370530</v>
+        <v>452640</v>
       </c>
       <c r="E1034" s="2" t="s">
         <v>2134</v>
@@ -41117,7 +41521,7 @@
         <v>1785</v>
       </c>
       <c r="D1134" s="4">
-        <v>566490</v>
+        <v>571320</v>
       </c>
       <c r="E1134" s="2" t="s">
         <v>3827</v>
@@ -41765,7 +42169,7 @@
         <v>1785</v>
       </c>
       <c r="D1161" s="4">
-        <v>246330</v>
+        <v>248400</v>
       </c>
       <c r="E1161" s="2" t="s">
         <v>631</v>
@@ -41981,7 +42385,7 @@
         <v>1785</v>
       </c>
       <c r="D1170" s="4">
-        <v>441600</v>
+        <v>445740</v>
       </c>
       <c r="E1170" s="2" t="s">
         <v>3827</v>
@@ -42557,7 +42961,7 @@
         <v>1785</v>
       </c>
       <c r="D1194" s="4">
-        <v>518880</v>
+        <v>523020</v>
       </c>
       <c r="E1194" s="2" t="s">
         <v>3827</v>
@@ -42917,7 +43321,7 @@
         <v>1785</v>
       </c>
       <c r="D1209" s="4">
-        <v>338790</v>
+        <v>341550</v>
       </c>
       <c r="E1209" s="2" t="s">
         <v>3827</v>
@@ -43013,7 +43417,7 @@
         <v>1785</v>
       </c>
       <c r="D1213" s="4">
-        <v>73830</v>
+        <v>74520</v>
       </c>
       <c r="E1213" s="2" t="s">
         <v>1863</v>
@@ -49613,7 +50017,7 @@
         <v>1785</v>
       </c>
       <c r="D1488" s="4">
-        <v>89010</v>
+        <v>89700</v>
       </c>
       <c r="E1488" s="2" t="s">
         <v>1863</v>
@@ -50357,7 +50761,7 @@
         <v>1785</v>
       </c>
       <c r="D1519" s="4">
-        <v>70035</v>
+        <v>70725</v>
       </c>
       <c r="E1519" s="2" t="s">
         <v>631</v>
@@ -50381,7 +50785,7 @@
         <v>1785</v>
       </c>
       <c r="D1520" s="4">
-        <v>59340</v>
+        <v>60030</v>
       </c>
       <c r="E1520" s="2" t="s">
         <v>1863</v>
@@ -56045,7 +56449,7 @@
         <v>152</v>
       </c>
       <c r="D1756" s="4">
-        <v>292300</v>
+        <v>310800</v>
       </c>
       <c r="E1756" s="2" t="s">
         <v>152</v>
@@ -56069,7 +56473,7 @@
         <v>152</v>
       </c>
       <c r="D1757" s="4">
-        <v>292300</v>
+        <v>310800</v>
       </c>
       <c r="E1757" s="2" t="s">
         <v>152</v>
@@ -56093,7 +56497,7 @@
         <v>152</v>
       </c>
       <c r="D1758" s="4">
-        <v>292300</v>
+        <v>310800</v>
       </c>
       <c r="E1758" s="2" t="s">
         <v>152</v>
@@ -57005,7 +57409,7 @@
         <v>1785</v>
       </c>
       <c r="D1796" s="4">
-        <v>140070</v>
+        <v>141450</v>
       </c>
       <c r="E1796" s="2" t="s">
         <v>3633</v>
@@ -57029,7 +57433,7 @@
         <v>1785</v>
       </c>
       <c r="D1797" s="4">
-        <v>143520</v>
+        <v>144900</v>
       </c>
       <c r="E1797" s="2" t="s">
         <v>3633</v>
@@ -57077,7 +57481,7 @@
         <v>1785</v>
       </c>
       <c r="D1799" s="4">
-        <v>40710</v>
+        <v>41055</v>
       </c>
       <c r="E1799" s="2" t="s">
         <v>3633</v>
@@ -57101,7 +57505,7 @@
         <v>1785</v>
       </c>
       <c r="D1800" s="4">
-        <v>40710</v>
+        <v>41055</v>
       </c>
       <c r="E1800" s="2" t="s">
         <v>3633</v>
@@ -57125,7 +57529,7 @@
         <v>1785</v>
       </c>
       <c r="D1801" s="4">
-        <v>143520</v>
+        <v>144900</v>
       </c>
       <c r="E1801" s="2" t="s">
         <v>3633</v>
@@ -57149,7 +57553,7 @@
         <v>1785</v>
       </c>
       <c r="D1802" s="4">
-        <v>416070</v>
+        <v>419520</v>
       </c>
       <c r="E1802" s="2" t="s">
         <v>3633</v>
@@ -57293,7 +57697,7 @@
         <v>1785</v>
       </c>
       <c r="D1808" s="4">
-        <v>126270</v>
+        <v>127650</v>
       </c>
       <c r="E1808" s="2" t="s">
         <v>3633</v>
@@ -57605,7 +58009,7 @@
         <v>1785</v>
       </c>
       <c r="D1821" s="4">
-        <v>301530</v>
+        <v>304290</v>
       </c>
       <c r="E1821" s="2" t="s">
         <v>3686</v>
@@ -57629,7 +58033,7 @@
         <v>1785</v>
       </c>
       <c r="D1822" s="4">
-        <v>489900</v>
+        <v>494040</v>
       </c>
       <c r="E1822" s="2" t="s">
         <v>3686</v>
@@ -57749,7 +58153,7 @@
         <v>1785</v>
       </c>
       <c r="D1827" s="4">
-        <v>81420</v>
+        <v>82110</v>
       </c>
       <c r="E1827" s="2" t="s">
         <v>1849</v>
@@ -57797,7 +58201,7 @@
         <v>1785</v>
       </c>
       <c r="D1829" s="4">
-        <v>81420</v>
+        <v>82110</v>
       </c>
       <c r="E1829" s="2" t="s">
         <v>1849</v>
@@ -57893,7 +58297,7 @@
         <v>1785</v>
       </c>
       <c r="D1833" s="4">
-        <v>111090</v>
+        <v>112125</v>
       </c>
       <c r="E1833" s="2" t="s">
         <v>3718</v>
@@ -58037,7 +58441,7 @@
         <v>1785</v>
       </c>
       <c r="D1839" s="4">
-        <v>147660</v>
+        <v>149040</v>
       </c>
       <c r="E1839" s="2" t="s">
         <v>3732</v>
@@ -58061,7 +58465,7 @@
         <v>1785</v>
       </c>
       <c r="D1840" s="4">
-        <v>151110</v>
+        <v>152490</v>
       </c>
       <c r="E1840" s="2" t="s">
         <v>3732</v>
@@ -58085,7 +58489,7 @@
         <v>1785</v>
       </c>
       <c r="D1841" s="4">
-        <v>250125</v>
+        <v>250815</v>
       </c>
       <c r="E1841" s="2" t="s">
         <v>3732</v>
@@ -58757,7 +59161,7 @@
         <v>1785</v>
       </c>
       <c r="D1869" s="4">
-        <v>91770</v>
+        <v>92460</v>
       </c>
       <c r="E1869" s="2" t="s">
         <v>3800</v>
@@ -58766,7 +59170,7 @@
         <v>1796</v>
       </c>
       <c r="G1869" s="2" t="s">
-        <v>324</v>
+        <v>11</v>
       </c>
       <c r="J1869" s="24"/>
     </row>
@@ -58790,7 +59194,7 @@
         <v>1802</v>
       </c>
       <c r="G1870" s="2" t="s">
-        <v>324</v>
+        <v>11</v>
       </c>
       <c r="J1870" s="24"/>
     </row>
@@ -58901,7 +59305,7 @@
         <v>1785</v>
       </c>
       <c r="D1875" s="4">
-        <v>111090</v>
+        <v>112125</v>
       </c>
       <c r="E1875" s="18" t="s">
         <v>3817</v>
@@ -58925,7 +59329,7 @@
         <v>1785</v>
       </c>
       <c r="D1876" s="4">
-        <v>37260</v>
+        <v>37605</v>
       </c>
       <c r="E1876" s="2" t="s">
         <v>3817</v>
@@ -59045,7 +59449,7 @@
         <v>1785</v>
       </c>
       <c r="D1881" s="4">
-        <v>84180</v>
+        <v>84870</v>
       </c>
       <c r="E1881" s="2" t="s">
         <v>3827</v>
@@ -59093,7 +59497,7 @@
         <v>1785</v>
       </c>
       <c r="D1883" s="4">
-        <v>145590</v>
+        <v>146280</v>
       </c>
       <c r="E1883" s="2" t="s">
         <v>3827</v>
@@ -59117,7 +59521,7 @@
         <v>1785</v>
       </c>
       <c r="D1884" s="4">
-        <v>153870</v>
+        <v>155250</v>
       </c>
       <c r="E1884" s="2" t="s">
         <v>3827</v>
@@ -59606,7 +60010,7 @@
         <v>3897</v>
       </c>
       <c r="G1904" s="2" t="s">
-        <v>324</v>
+        <v>11</v>
       </c>
       <c r="J1904" s="24"/>
     </row>
@@ -59765,7 +60169,7 @@
         <v>1785</v>
       </c>
       <c r="D1911" s="20">
-        <v>231150</v>
+        <v>233220</v>
       </c>
       <c r="E1911" s="2" t="s">
         <v>3905</v>
@@ -59789,7 +60193,7 @@
         <v>1785</v>
       </c>
       <c r="D1912" s="20">
-        <v>262200</v>
+        <v>264960</v>
       </c>
       <c r="E1912" s="2" t="s">
         <v>3906</v>
@@ -59813,7 +60217,7 @@
         <v>1785</v>
       </c>
       <c r="D1913" s="20">
-        <v>231150</v>
+        <v>233220</v>
       </c>
       <c r="E1913" s="2" t="s">
         <v>3905</v>
@@ -59837,7 +60241,7 @@
         <v>1785</v>
       </c>
       <c r="D1914" s="20">
-        <v>262200</v>
+        <v>264960</v>
       </c>
       <c r="E1914" s="2" t="s">
         <v>3906</v>
@@ -59861,7 +60265,7 @@
         <v>1785</v>
       </c>
       <c r="D1915" s="20">
-        <v>293250</v>
+        <v>296700</v>
       </c>
       <c r="E1915" s="2" t="s">
         <v>3907</v>
@@ -60389,7 +60793,7 @@
         <v>9</v>
       </c>
       <c r="D1937" s="20">
-        <v>88500</v>
+        <v>89090</v>
       </c>
       <c r="E1937" s="2" t="s">
         <v>10</v>
@@ -60941,7 +61345,7 @@
         <v>1785</v>
       </c>
       <c r="D1960" s="20">
-        <v>242190</v>
+        <v>242880</v>
       </c>
       <c r="E1960" s="2" t="s">
         <v>4011</v>
@@ -60965,7 +61369,7 @@
         <v>1785</v>
       </c>
       <c r="D1961" s="20">
-        <v>129720</v>
+        <v>131100</v>
       </c>
       <c r="E1961" s="2" t="s">
         <v>4011</v>
@@ -60989,7 +61393,7 @@
         <v>1785</v>
       </c>
       <c r="D1962" s="20">
-        <v>110400</v>
+        <v>111435</v>
       </c>
       <c r="E1962" s="2" t="s">
         <v>4011</v>
@@ -61013,7 +61417,7 @@
         <v>1785</v>
       </c>
       <c r="D1963" s="20">
-        <v>40710</v>
+        <v>41400</v>
       </c>
       <c r="E1963" s="2" t="s">
         <v>4012</v>
@@ -61037,7 +61441,7 @@
         <v>1785</v>
       </c>
       <c r="D1964" s="20">
-        <v>40710</v>
+        <v>41400</v>
       </c>
       <c r="E1964" s="2" t="s">
         <v>4012</v>
@@ -61061,7 +61465,7 @@
         <v>1785</v>
       </c>
       <c r="D1965" s="20">
-        <v>40710</v>
+        <v>41400</v>
       </c>
       <c r="E1965" s="2" t="s">
         <v>4012</v>
@@ -61085,7 +61489,7 @@
         <v>1785</v>
       </c>
       <c r="D1966" s="20">
-        <v>40710</v>
+        <v>41400</v>
       </c>
       <c r="E1966" s="2" t="s">
         <v>4012</v>
@@ -62117,7 +62521,7 @@
         <v>1785</v>
       </c>
       <c r="D2009" s="4">
-        <v>147315</v>
+        <v>148005</v>
       </c>
       <c r="E2009" s="2" t="s">
         <v>4104</v>
@@ -62141,7 +62545,7 @@
         <v>1785</v>
       </c>
       <c r="D2010" s="4">
-        <v>59340</v>
+        <v>60030</v>
       </c>
       <c r="E2010" s="2" t="s">
         <v>4103</v>
@@ -62165,7 +62569,7 @@
         <v>1785</v>
       </c>
       <c r="D2011" s="4">
-        <v>112125</v>
+        <v>112815</v>
       </c>
       <c r="E2011" s="2" t="s">
         <v>4103</v>
@@ -62189,7 +62593,7 @@
         <v>1785</v>
       </c>
       <c r="D2012" s="4">
-        <v>73830</v>
+        <v>74520</v>
       </c>
       <c r="E2012" s="2" t="s">
         <v>1827</v>
@@ -62573,7 +62977,7 @@
         <v>1785</v>
       </c>
       <c r="D2028" s="20">
-        <v>3034000</v>
+        <v>3700000</v>
       </c>
       <c r="E2028" s="2" t="s">
         <v>4149</v>
@@ -62597,7 +63001,7 @@
         <v>1785</v>
       </c>
       <c r="D2029" s="20">
-        <v>4736000</v>
+        <v>5846000</v>
       </c>
       <c r="E2029" s="2" t="s">
         <v>4149</v>
@@ -62645,7 +63049,7 @@
         <v>1785</v>
       </c>
       <c r="D2031" s="20">
-        <v>599400</v>
+        <v>740000</v>
       </c>
       <c r="E2031" s="2" t="s">
         <v>4149</v>
@@ -62885,7 +63289,7 @@
         <v>1785</v>
       </c>
       <c r="D2041" s="20">
-        <v>68310</v>
+        <v>69000</v>
       </c>
       <c r="E2041" s="2" t="s">
         <v>4219</v>
@@ -62909,7 +63313,7 @@
         <v>1785</v>
       </c>
       <c r="D2042" s="20">
-        <v>68310</v>
+        <v>69000</v>
       </c>
       <c r="E2042" s="2" t="s">
         <v>4219</v>
@@ -62933,7 +63337,7 @@
         <v>1785</v>
       </c>
       <c r="D2043" s="20">
-        <v>68310</v>
+        <v>69000</v>
       </c>
       <c r="E2043" s="2" t="s">
         <v>4219</v>
@@ -62957,7 +63361,7 @@
         <v>1785</v>
       </c>
       <c r="D2044" s="20">
-        <v>94530</v>
+        <v>95565</v>
       </c>
       <c r="E2044" s="2" t="s">
         <v>4219</v>
@@ -62981,7 +63385,7 @@
         <v>1785</v>
       </c>
       <c r="D2045" s="20">
-        <v>94530</v>
+        <v>95565</v>
       </c>
       <c r="E2045" s="2" t="s">
         <v>4219</v>
@@ -63005,7 +63409,7 @@
         <v>1785</v>
       </c>
       <c r="D2046" s="20">
-        <v>94530</v>
+        <v>95565</v>
       </c>
       <c r="E2046" s="2" t="s">
         <v>4219</v>
@@ -63029,7 +63433,7 @@
         <v>1785</v>
       </c>
       <c r="D2047" s="20">
-        <v>131790</v>
+        <v>133170</v>
       </c>
       <c r="E2047" s="2" t="s">
         <v>4219</v>
@@ -63053,7 +63457,7 @@
         <v>1785</v>
       </c>
       <c r="D2048" s="20">
-        <v>131790</v>
+        <v>133170</v>
       </c>
       <c r="E2048" s="2" t="s">
         <v>4219</v>
@@ -63077,7 +63481,7 @@
         <v>1785</v>
       </c>
       <c r="D2049" s="20">
-        <v>131790</v>
+        <v>133170</v>
       </c>
       <c r="E2049" s="2" t="s">
         <v>4219</v>
@@ -63125,7 +63529,7 @@
         <v>1785</v>
       </c>
       <c r="D2051" s="20">
-        <v>64860</v>
+        <v>65550</v>
       </c>
       <c r="E2051" s="2" t="s">
         <v>4219</v>
@@ -63149,7 +63553,7 @@
         <v>1785</v>
       </c>
       <c r="D2052" s="20">
-        <v>64860</v>
+        <v>65550</v>
       </c>
       <c r="E2052" s="2" t="s">
         <v>4219</v>
@@ -63173,7 +63577,7 @@
         <v>1785</v>
       </c>
       <c r="D2053" s="20">
-        <v>41400</v>
+        <v>41745</v>
       </c>
       <c r="E2053" s="2" t="s">
         <v>4219</v>
@@ -63197,7 +63601,7 @@
         <v>1785</v>
       </c>
       <c r="D2054" s="20">
-        <v>41400</v>
+        <v>41745</v>
       </c>
       <c r="E2054" s="2" t="s">
         <v>4219</v>
@@ -63221,7 +63625,7 @@
         <v>1785</v>
       </c>
       <c r="D2055" s="20">
-        <v>41400</v>
+        <v>41745</v>
       </c>
       <c r="E2055" s="2" t="s">
         <v>4219</v>
@@ -63245,7 +63649,7 @@
         <v>1785</v>
       </c>
       <c r="D2056" s="20">
-        <v>95565</v>
+        <v>96600</v>
       </c>
       <c r="E2056" s="2" t="s">
         <v>4219</v>
@@ -63269,7 +63673,7 @@
         <v>1785</v>
       </c>
       <c r="D2057" s="20">
-        <v>95565</v>
+        <v>96600</v>
       </c>
       <c r="E2057" s="2" t="s">
         <v>4219</v>
@@ -63293,7 +63697,7 @@
         <v>1785</v>
       </c>
       <c r="D2058" s="20">
-        <v>95565</v>
+        <v>96600</v>
       </c>
       <c r="E2058" s="2" t="s">
         <v>4219</v>
@@ -63317,7 +63721,7 @@
         <v>1785</v>
       </c>
       <c r="D2059" s="20">
-        <v>256680</v>
+        <v>258060</v>
       </c>
       <c r="E2059" s="2" t="s">
         <v>4219</v>
@@ -64349,7 +64753,7 @@
         <v>1785</v>
       </c>
       <c r="D2102" s="20">
-        <v>420900</v>
+        <v>422970</v>
       </c>
       <c r="E2102" s="2" t="s">
         <v>3633</v>
@@ -64373,7 +64777,7 @@
         <v>1785</v>
       </c>
       <c r="D2103" s="20">
-        <v>169050</v>
+        <v>170775</v>
       </c>
       <c r="E2103" s="2" t="s">
         <v>3633</v>
@@ -64397,7 +64801,7 @@
         <v>1785</v>
       </c>
       <c r="D2104" s="20">
-        <v>65550</v>
+        <v>66240</v>
       </c>
       <c r="E2104" s="2" t="s">
         <v>3633</v>
@@ -64949,7 +65353,7 @@
         <v>1785</v>
       </c>
       <c r="D2127" s="20">
-        <v>169050</v>
+        <v>170430</v>
       </c>
       <c r="E2127" s="2" t="s">
         <v>4346</v>
@@ -64997,7 +65401,7 @@
         <v>1785</v>
       </c>
       <c r="D2129" s="20">
-        <v>68310</v>
+        <v>69000</v>
       </c>
       <c r="E2129" s="2" t="s">
         <v>4359</v>
@@ -65021,7 +65425,7 @@
         <v>1785</v>
       </c>
       <c r="D2130" s="20">
-        <v>68310</v>
+        <v>69000</v>
       </c>
       <c r="E2130" s="2" t="s">
         <v>3633</v>
@@ -65404,13 +65808,13 @@
     </row>
     <row r="2147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2147" s="2" t="s">
-        <v>4407</v>
+        <v>4393</v>
       </c>
       <c r="B2147" s="2" t="s">
-        <v>4406</v>
+        <v>4392</v>
       </c>
       <c r="C2147" s="2" t="s">
-        <v>1785</v>
+        <v>9</v>
       </c>
       <c r="D2147" s="20">
         <v>153400</v>
@@ -65427,13 +65831,13 @@
     </row>
     <row r="2148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2148" s="2" t="s">
-        <v>4409</v>
+        <v>4395</v>
       </c>
       <c r="B2148" s="2" t="s">
-        <v>4408</v>
+        <v>4394</v>
       </c>
       <c r="C2148" s="2" t="s">
-        <v>4392</v>
+        <v>9</v>
       </c>
       <c r="D2148" s="20">
         <v>153400</v>
@@ -65450,13 +65854,13 @@
     </row>
     <row r="2149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2149" s="2" t="s">
-        <v>4411</v>
+        <v>4397</v>
       </c>
       <c r="B2149" s="2" t="s">
-        <v>4410</v>
+        <v>4396</v>
       </c>
       <c r="C2149" s="2" t="s">
-        <v>4393</v>
+        <v>9</v>
       </c>
       <c r="D2149" s="20">
         <v>153400</v>
@@ -65473,13 +65877,13 @@
     </row>
     <row r="2150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2150" s="2" t="s">
-        <v>4413</v>
+        <v>4399</v>
       </c>
       <c r="B2150" s="2" t="s">
-        <v>4412</v>
+        <v>4398</v>
       </c>
       <c r="C2150" s="2" t="s">
-        <v>4394</v>
+        <v>9</v>
       </c>
       <c r="D2150" s="20">
         <v>153400</v>
@@ -65496,13 +65900,13 @@
     </row>
     <row r="2151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2151" s="2" t="s">
-        <v>4415</v>
+        <v>4401</v>
       </c>
       <c r="B2151" s="2" t="s">
-        <v>4414</v>
+        <v>4400</v>
       </c>
       <c r="C2151" s="2" t="s">
-        <v>4395</v>
+        <v>9</v>
       </c>
       <c r="D2151" s="20">
         <v>153400</v>
@@ -65519,13 +65923,13 @@
     </row>
     <row r="2152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2152" s="2" t="s">
-        <v>4417</v>
+        <v>4403</v>
       </c>
       <c r="B2152" s="2" t="s">
-        <v>4416</v>
+        <v>4402</v>
       </c>
       <c r="C2152" s="2" t="s">
-        <v>4396</v>
+        <v>9</v>
       </c>
       <c r="D2152" s="20">
         <v>153400</v>
@@ -65542,13 +65946,13 @@
     </row>
     <row r="2153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2153" s="2" t="s">
-        <v>4419</v>
+        <v>4405</v>
       </c>
       <c r="B2153" s="2" t="s">
-        <v>4418</v>
+        <v>4404</v>
       </c>
       <c r="C2153" s="2" t="s">
-        <v>4397</v>
+        <v>9</v>
       </c>
       <c r="D2153" s="20">
         <v>153400</v>
@@ -65565,13 +65969,13 @@
     </row>
     <row r="2154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2154" s="2" t="s">
-        <v>4421</v>
+        <v>4407</v>
       </c>
       <c r="B2154" s="2" t="s">
-        <v>4420</v>
+        <v>4406</v>
       </c>
       <c r="C2154" s="2" t="s">
-        <v>4398</v>
+        <v>9</v>
       </c>
       <c r="D2154" s="20">
         <v>153400</v>
@@ -65588,13 +65992,13 @@
     </row>
     <row r="2155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2155" s="2" t="s">
-        <v>4423</v>
+        <v>4409</v>
       </c>
       <c r="B2155" s="2" t="s">
-        <v>4422</v>
+        <v>4408</v>
       </c>
       <c r="C2155" s="2" t="s">
-        <v>4399</v>
+        <v>9</v>
       </c>
       <c r="D2155" s="20">
         <v>153400</v>
@@ -65611,13 +66015,13 @@
     </row>
     <row r="2156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2156" s="2" t="s">
-        <v>4425</v>
+        <v>4411</v>
       </c>
       <c r="B2156" s="2" t="s">
-        <v>4424</v>
+        <v>4410</v>
       </c>
       <c r="C2156" s="2" t="s">
-        <v>4400</v>
+        <v>9</v>
       </c>
       <c r="D2156" s="20">
         <v>153400</v>
@@ -65634,13 +66038,13 @@
     </row>
     <row r="2157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2157" s="2" t="s">
-        <v>4427</v>
+        <v>4417</v>
       </c>
       <c r="B2157" s="2" t="s">
-        <v>4426</v>
+        <v>4412</v>
       </c>
       <c r="C2157" s="2" t="s">
-        <v>4401</v>
+        <v>9</v>
       </c>
       <c r="D2157" s="20">
         <v>153400</v>
@@ -65657,13 +66061,13 @@
     </row>
     <row r="2158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2158" s="2" t="s">
-        <v>4429</v>
+        <v>4418</v>
       </c>
       <c r="B2158" s="2" t="s">
-        <v>4428</v>
+        <v>4413</v>
       </c>
       <c r="C2158" s="2" t="s">
-        <v>4402</v>
+        <v>9</v>
       </c>
       <c r="D2158" s="20">
         <v>153400</v>
@@ -65680,13 +66084,13 @@
     </row>
     <row r="2159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2159" s="2" t="s">
-        <v>4431</v>
+        <v>4419</v>
       </c>
       <c r="B2159" s="2" t="s">
-        <v>4430</v>
+        <v>4414</v>
       </c>
       <c r="C2159" s="2" t="s">
-        <v>4403</v>
+        <v>9</v>
       </c>
       <c r="D2159" s="20">
         <v>153400</v>
@@ -65703,13 +66107,13 @@
     </row>
     <row r="2160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2160" s="2" t="s">
-        <v>4433</v>
+        <v>4420</v>
       </c>
       <c r="B2160" s="2" t="s">
-        <v>4432</v>
+        <v>4415</v>
       </c>
       <c r="C2160" s="2" t="s">
-        <v>4404</v>
+        <v>9</v>
       </c>
       <c r="D2160" s="20">
         <v>153400</v>
@@ -65726,13 +66130,13 @@
     </row>
     <row r="2161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2161" s="2" t="s">
-        <v>4435</v>
+        <v>4421</v>
       </c>
       <c r="B2161" s="2" t="s">
-        <v>4434</v>
+        <v>4416</v>
       </c>
       <c r="C2161" s="2" t="s">
-        <v>4405</v>
+        <v>9</v>
       </c>
       <c r="D2161" s="20">
         <v>153400</v>
@@ -65744,6 +66148,1476 @@
         <v>10</v>
       </c>
       <c r="G2161" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2162" s="2" t="s">
+        <v>4422</v>
+      </c>
+      <c r="B2162" s="2" t="s">
+        <v>4423</v>
+      </c>
+      <c r="C2162" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2162" s="20">
+        <v>233100</v>
+      </c>
+      <c r="E2162" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2162" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G2162" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2163" s="2" t="s">
+        <v>4424</v>
+      </c>
+      <c r="B2163" s="2" t="s">
+        <v>4425</v>
+      </c>
+      <c r="C2163" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2163" s="20">
+        <v>2212000</v>
+      </c>
+      <c r="E2163" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2163" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2163" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2164" s="2" t="s">
+        <v>4426</v>
+      </c>
+      <c r="B2164" s="2" t="s">
+        <v>4427</v>
+      </c>
+      <c r="C2164" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2164" s="20">
+        <v>3555000</v>
+      </c>
+      <c r="E2164" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2164" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2164" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2165" s="2" t="s">
+        <v>4428</v>
+      </c>
+      <c r="B2165" s="2" t="s">
+        <v>4429</v>
+      </c>
+      <c r="C2165" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2165" s="20">
+        <v>261165</v>
+      </c>
+      <c r="E2165" s="2" t="s">
+        <v>4103</v>
+      </c>
+      <c r="F2165" s="2" t="s">
+        <v>2042</v>
+      </c>
+      <c r="G2165" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2166" s="2" t="s">
+        <v>4430</v>
+      </c>
+      <c r="B2166" s="2" t="s">
+        <v>4431</v>
+      </c>
+      <c r="C2166" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2166" s="20">
+        <v>320850</v>
+      </c>
+      <c r="E2166" s="2" t="s">
+        <v>4103</v>
+      </c>
+      <c r="F2166" s="2" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G2166" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2167" s="2" t="s">
+        <v>4432</v>
+      </c>
+      <c r="B2167" s="2" t="s">
+        <v>4433</v>
+      </c>
+      <c r="C2167" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2167" s="20">
+        <v>233100</v>
+      </c>
+      <c r="E2167" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2167" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G2167" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2168" s="2" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B2168" s="2" t="s">
+        <v>4435</v>
+      </c>
+      <c r="C2168" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2168" s="20">
+        <v>35400</v>
+      </c>
+      <c r="E2168" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2168" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2168" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2169" s="2" t="s">
+        <v>4436</v>
+      </c>
+      <c r="B2169" s="2" t="s">
+        <v>4437</v>
+      </c>
+      <c r="C2169" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2169" s="20">
+        <v>35400</v>
+      </c>
+      <c r="E2169" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2169" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2169" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2170" s="2" t="s">
+        <v>4438</v>
+      </c>
+      <c r="B2170" s="2" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C2170" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2170" s="20">
+        <v>189750</v>
+      </c>
+      <c r="E2170" s="2" t="s">
+        <v>3800</v>
+      </c>
+      <c r="F2170" s="2" t="s">
+        <v>4439</v>
+      </c>
+      <c r="G2170" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2171" s="2" t="s">
+        <v>4440</v>
+      </c>
+      <c r="B2171" s="2" t="s">
+        <v>4441</v>
+      </c>
+      <c r="C2171" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2171" s="20">
+        <v>84870</v>
+      </c>
+      <c r="E2171" s="2" t="s">
+        <v>3800</v>
+      </c>
+      <c r="F2171" s="2" t="str">
+        <f>B2171</f>
+        <v xml:space="preserve">Air Scoop </v>
+      </c>
+      <c r="G2171" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2172" s="2" t="s">
+        <v>4442</v>
+      </c>
+      <c r="B2172" s="2" t="s">
+        <v>4443</v>
+      </c>
+      <c r="C2172" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2172" s="20">
+        <v>110400</v>
+      </c>
+      <c r="E2172" s="2" t="s">
+        <v>3800</v>
+      </c>
+      <c r="F2172" s="2" t="str">
+        <f t="shared" ref="F2172:F2175" si="0">B2172</f>
+        <v>Rear Pad</v>
+      </c>
+      <c r="G2172" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2173" s="2" t="s">
+        <v>4444</v>
+      </c>
+      <c r="B2173" s="2" t="s">
+        <v>4445</v>
+      </c>
+      <c r="C2173" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2173" s="20">
+        <v>420900</v>
+      </c>
+      <c r="E2173" s="2" t="s">
+        <v>3800</v>
+      </c>
+      <c r="F2173" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Panel Step Floor</v>
+      </c>
+      <c r="G2173" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2174" s="2" t="s">
+        <v>4446</v>
+      </c>
+      <c r="B2174" s="2" t="s">
+        <v>4447</v>
+      </c>
+      <c r="C2174" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2174" s="20">
+        <v>156630</v>
+      </c>
+      <c r="E2174" s="2" t="s">
+        <v>3800</v>
+      </c>
+      <c r="F2174" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Garnish Front</v>
+      </c>
+      <c r="G2174" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2175" s="2" t="s">
+        <v>4448</v>
+      </c>
+      <c r="B2175" s="2" t="s">
+        <v>4449</v>
+      </c>
+      <c r="C2175" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2175" s="20">
+        <v>91080</v>
+      </c>
+      <c r="E2175" s="2" t="s">
+        <v>3800</v>
+      </c>
+      <c r="F2175" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Side Pad Rubber</v>
+      </c>
+      <c r="G2175" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2176" s="2" t="s">
+        <v>4450</v>
+      </c>
+      <c r="B2176" s="2" t="s">
+        <v>4451</v>
+      </c>
+      <c r="C2176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2176" s="20">
+        <v>330400</v>
+      </c>
+      <c r="E2176" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2176" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2176" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2177" s="2" t="s">
+        <v>4452</v>
+      </c>
+      <c r="B2177" s="2" t="s">
+        <v>4453</v>
+      </c>
+      <c r="C2177" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2177" s="20">
+        <v>330400</v>
+      </c>
+      <c r="E2177" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2177" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2177" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2178" s="2" t="s">
+        <v>4454</v>
+      </c>
+      <c r="B2178" s="2" t="s">
+        <v>4455</v>
+      </c>
+      <c r="C2178" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2178" s="20">
+        <v>330400</v>
+      </c>
+      <c r="E2178" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2178" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2178" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2179" s="2" t="s">
+        <v>4456</v>
+      </c>
+      <c r="B2179" s="2" t="s">
+        <v>4457</v>
+      </c>
+      <c r="C2179" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2179" s="20">
+        <v>330400</v>
+      </c>
+      <c r="E2179" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2179" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2179" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2180" s="2" t="s">
+        <v>4458</v>
+      </c>
+      <c r="B2180" s="2" t="s">
+        <v>4459</v>
+      </c>
+      <c r="C2180" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2180" s="20">
+        <v>330400</v>
+      </c>
+      <c r="E2180" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2180" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2180" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2181" s="2" t="s">
+        <v>4460</v>
+      </c>
+      <c r="B2181" s="2" t="s">
+        <v>4461</v>
+      </c>
+      <c r="C2181" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2181" s="20">
+        <v>330400</v>
+      </c>
+      <c r="E2181" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2181" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2181" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2182" s="2" t="s">
+        <v>4462</v>
+      </c>
+      <c r="B2182" s="2" t="s">
+        <v>4463</v>
+      </c>
+      <c r="C2182" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2182" s="20">
+        <v>330400</v>
+      </c>
+      <c r="E2182" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2182" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2182" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2183" s="2" t="s">
+        <v>4464</v>
+      </c>
+      <c r="B2183" s="2" t="s">
+        <v>4465</v>
+      </c>
+      <c r="C2183" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2183" s="20">
+        <v>330400</v>
+      </c>
+      <c r="E2183" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2183" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2183" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2184" s="2" t="s">
+        <v>4466</v>
+      </c>
+      <c r="B2184" s="2" t="s">
+        <v>4467</v>
+      </c>
+      <c r="C2184" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2184" s="20">
+        <v>206500</v>
+      </c>
+      <c r="E2184" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2184" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2184" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2185" s="2" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B2185" s="2" t="s">
+        <v>4469</v>
+      </c>
+      <c r="C2185" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2185" s="20">
+        <v>206500</v>
+      </c>
+      <c r="E2185" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2185" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2185" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2186" s="2" t="s">
+        <v>4470</v>
+      </c>
+      <c r="B2186" s="2" t="s">
+        <v>4471</v>
+      </c>
+      <c r="C2186" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2186" s="20">
+        <v>206500</v>
+      </c>
+      <c r="E2186" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2186" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2186" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2187" s="2" t="s">
+        <v>4472</v>
+      </c>
+      <c r="B2187" s="2" t="s">
+        <v>4473</v>
+      </c>
+      <c r="C2187" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2187" s="20">
+        <v>280250</v>
+      </c>
+      <c r="E2187" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2187" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2187" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2188" s="2" t="s">
+        <v>4474</v>
+      </c>
+      <c r="B2188" s="2" t="s">
+        <v>4475</v>
+      </c>
+      <c r="C2188" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2188" s="20">
+        <v>379500</v>
+      </c>
+      <c r="E2188" s="2" t="s">
+        <v>4476</v>
+      </c>
+      <c r="F2188" s="2" t="str">
+        <f t="shared" ref="F2188:F2203" si="1">B2188</f>
+        <v>REAR RACK SCOOPY</v>
+      </c>
+      <c r="G2188" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2189" s="2" t="s">
+        <v>4477</v>
+      </c>
+      <c r="B2189" s="2" t="s">
+        <v>4478</v>
+      </c>
+      <c r="C2189" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2189" s="20">
+        <v>155250</v>
+      </c>
+      <c r="E2189" s="2" t="s">
+        <v>4476</v>
+      </c>
+      <c r="F2189" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>WIND SCREEN SCOOPY</v>
+      </c>
+      <c r="G2189" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2190" s="2" t="s">
+        <v>4479</v>
+      </c>
+      <c r="B2190" s="2" t="s">
+        <v>4480</v>
+      </c>
+      <c r="C2190" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2190" s="20">
+        <v>103500</v>
+      </c>
+      <c r="E2190" s="2" t="s">
+        <v>4476</v>
+      </c>
+      <c r="F2190" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>STICKER SET RED SCOOPY</v>
+      </c>
+      <c r="G2190" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2191" s="2" t="s">
+        <v>4481</v>
+      </c>
+      <c r="B2191" s="2" t="s">
+        <v>4482</v>
+      </c>
+      <c r="C2191" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2191" s="20">
+        <v>103500</v>
+      </c>
+      <c r="E2191" s="2" t="s">
+        <v>4476</v>
+      </c>
+      <c r="F2191" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>STICKER SET BLACK SCOOPY</v>
+      </c>
+      <c r="G2191" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2192" s="2" t="s">
+        <v>4483</v>
+      </c>
+      <c r="B2192" s="2" t="s">
+        <v>4484</v>
+      </c>
+      <c r="C2192" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2192" s="20">
+        <v>103500</v>
+      </c>
+      <c r="E2192" s="2" t="s">
+        <v>4476</v>
+      </c>
+      <c r="F2192" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>STICKER SET MINT SCOOPY</v>
+      </c>
+      <c r="G2192" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2193" s="2" t="s">
+        <v>4485</v>
+      </c>
+      <c r="B2193" s="2" t="s">
+        <v>4486</v>
+      </c>
+      <c r="C2193" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2193" s="20">
+        <v>103500</v>
+      </c>
+      <c r="E2193" s="2" t="s">
+        <v>4476</v>
+      </c>
+      <c r="F2193" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>STICKER SET CREAM SCOOPY</v>
+      </c>
+      <c r="G2193" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2194" s="2" t="s">
+        <v>4487</v>
+      </c>
+      <c r="B2194" s="2" t="s">
+        <v>4488</v>
+      </c>
+      <c r="C2194" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2194" s="20">
+        <v>112125</v>
+      </c>
+      <c r="E2194" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F2194" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>SEAT COVER GENIO</v>
+      </c>
+      <c r="G2194" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2195" s="2" t="s">
+        <v>4489</v>
+      </c>
+      <c r="B2195" s="2" t="s">
+        <v>4490</v>
+      </c>
+      <c r="C2195" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2195" s="20">
+        <v>106950</v>
+      </c>
+      <c r="E2195" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F2195" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>GARNISH MUFFLER GENIO YLW</v>
+      </c>
+      <c r="G2195" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2196" s="2" t="s">
+        <v>4491</v>
+      </c>
+      <c r="B2196" s="2" t="s">
+        <v>4492</v>
+      </c>
+      <c r="C2196" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2196" s="20">
+        <v>106950</v>
+      </c>
+      <c r="E2196" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F2196" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>GARNISH MUFFLER GENIO WHT</v>
+      </c>
+      <c r="G2196" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2197" s="2" t="s">
+        <v>4493</v>
+      </c>
+      <c r="B2197" s="2" t="s">
+        <v>4494</v>
+      </c>
+      <c r="C2197" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2197" s="20">
+        <v>84870</v>
+      </c>
+      <c r="E2197" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F2197" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>GARN PANEL MTR GENIO YLW</v>
+      </c>
+      <c r="G2197" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2198" s="2" t="s">
+        <v>4495</v>
+      </c>
+      <c r="B2198" s="2" t="s">
+        <v>4496</v>
+      </c>
+      <c r="C2198" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2198" s="20">
+        <v>84870</v>
+      </c>
+      <c r="E2198" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F2198" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>GARN PANEL MTR GENIO WHT</v>
+      </c>
+      <c r="G2198" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2199" s="2" t="s">
+        <v>4497</v>
+      </c>
+      <c r="B2199" s="2" t="s">
+        <v>4498</v>
+      </c>
+      <c r="C2199" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2199" s="20">
+        <v>60030</v>
+      </c>
+      <c r="E2199" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F2199" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>GARN FAN COVER GENIO YLW</v>
+      </c>
+      <c r="G2199" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2200" s="2" t="s">
+        <v>4499</v>
+      </c>
+      <c r="B2200" s="2" t="s">
+        <v>4500</v>
+      </c>
+      <c r="C2200" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2200" s="20">
+        <v>60030</v>
+      </c>
+      <c r="E2200" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F2200" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>GARN FAN COVER GENIO WHT</v>
+      </c>
+      <c r="G2200" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2201" s="2" t="s">
+        <v>4501</v>
+      </c>
+      <c r="B2201" s="2" t="s">
+        <v>4502</v>
+      </c>
+      <c r="C2201" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2201" s="20">
+        <v>60030</v>
+      </c>
+      <c r="E2201" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F2201" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>GRN AIR CLEANER GENIO YLW</v>
+      </c>
+      <c r="G2201" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2202" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="B2202" s="2" t="s">
+        <v>4504</v>
+      </c>
+      <c r="C2202" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2202" s="20">
+        <v>60030</v>
+      </c>
+      <c r="E2202" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F2202" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>GRN AIR CLEANER GENIO WHT</v>
+      </c>
+      <c r="G2202" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2203" s="2" t="s">
+        <v>4487</v>
+      </c>
+      <c r="B2203" s="2" t="s">
+        <v>4488</v>
+      </c>
+      <c r="C2203" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2203" s="20">
+        <v>112125</v>
+      </c>
+      <c r="E2203" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F2203" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>SEAT COVER GENIO</v>
+      </c>
+      <c r="G2203" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2204" s="2" t="s">
+        <v>4505</v>
+      </c>
+      <c r="B2204" s="2" t="s">
+        <v>4506</v>
+      </c>
+      <c r="C2204" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2204" s="20">
+        <v>64900</v>
+      </c>
+      <c r="E2204" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2204" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2204" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2205" s="2" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B2205" s="2" t="s">
+        <v>4508</v>
+      </c>
+      <c r="C2205" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2205" s="20">
+        <v>206500</v>
+      </c>
+      <c r="E2205" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2205" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2205" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2206" s="2" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B2206" s="2" t="s">
+        <v>4510</v>
+      </c>
+      <c r="C2206" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2206" s="20">
+        <v>206500</v>
+      </c>
+      <c r="E2206" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2206" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2206" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2207" s="2" t="s">
+        <v>4511</v>
+      </c>
+      <c r="B2207" s="2" t="s">
+        <v>4512</v>
+      </c>
+      <c r="C2207" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2207" s="20">
+        <v>206500</v>
+      </c>
+      <c r="E2207" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2207" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2207" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2208" s="2" t="s">
+        <v>4513</v>
+      </c>
+      <c r="B2208" s="2" t="s">
+        <v>4514</v>
+      </c>
+      <c r="C2208" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2208" s="20">
+        <v>206500</v>
+      </c>
+      <c r="E2208" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2208" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2208" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2209" s="2" t="s">
+        <v>4515</v>
+      </c>
+      <c r="B2209" s="2" t="s">
+        <v>4516</v>
+      </c>
+      <c r="C2209" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2209" s="20">
+        <v>206500</v>
+      </c>
+      <c r="E2209" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2209" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2209" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2210" s="2" t="s">
+        <v>4517</v>
+      </c>
+      <c r="B2210" s="2" t="s">
+        <v>4518</v>
+      </c>
+      <c r="C2210" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2210" s="20">
+        <v>212400</v>
+      </c>
+      <c r="E2210" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2210" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2210" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2211" s="2" t="s">
+        <v>4519</v>
+      </c>
+      <c r="B2211" s="2" t="s">
+        <v>4520</v>
+      </c>
+      <c r="C2211" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2211" s="20">
+        <v>212400</v>
+      </c>
+      <c r="E2211" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2211" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2211" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2212" s="2" t="s">
+        <v>4521</v>
+      </c>
+      <c r="B2212" s="2" t="s">
+        <v>4522</v>
+      </c>
+      <c r="C2212" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2212" s="20">
+        <v>212400</v>
+      </c>
+      <c r="E2212" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2212" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2212" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2213" s="2" t="s">
+        <v>4523</v>
+      </c>
+      <c r="B2213" s="2" t="s">
+        <v>4524</v>
+      </c>
+      <c r="C2213" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2213" s="20">
+        <v>212400</v>
+      </c>
+      <c r="E2213" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2213" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2213" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2214" s="2" t="s">
+        <v>4525</v>
+      </c>
+      <c r="B2214" s="2" t="s">
+        <v>4526</v>
+      </c>
+      <c r="C2214" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2214" s="20">
+        <v>212400</v>
+      </c>
+      <c r="E2214" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2214" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2214" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2215" s="2" t="s">
+        <v>4527</v>
+      </c>
+      <c r="B2215" s="2" t="s">
+        <v>4528</v>
+      </c>
+      <c r="C2215" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2215" s="20">
+        <v>177000</v>
+      </c>
+      <c r="E2215" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2215" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2215" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2216" s="2" t="s">
+        <v>4529</v>
+      </c>
+      <c r="B2216" s="2" t="s">
+        <v>4530</v>
+      </c>
+      <c r="C2216" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2216" s="20">
+        <v>88500</v>
+      </c>
+      <c r="E2216" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2216" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2216" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2217" s="2" t="s">
+        <v>4531</v>
+      </c>
+      <c r="B2217" s="2" t="s">
+        <v>4532</v>
+      </c>
+      <c r="C2217" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2217" s="20">
+        <v>162250</v>
+      </c>
+      <c r="E2217" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2217" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2217" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2218" s="2" t="s">
+        <v>4533</v>
+      </c>
+      <c r="B2218" s="2" t="s">
+        <v>4534</v>
+      </c>
+      <c r="C2218" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2218" s="20">
+        <v>162250</v>
+      </c>
+      <c r="E2218" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2218" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2218" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2219" s="2" t="s">
+        <v>4535</v>
+      </c>
+      <c r="B2219" s="2" t="s">
+        <v>4536</v>
+      </c>
+      <c r="C2219" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2219" s="20">
+        <v>162250</v>
+      </c>
+      <c r="E2219" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2219" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2219" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2220" s="2" t="s">
+        <v>4537</v>
+      </c>
+      <c r="B2220" s="2" t="s">
+        <v>4538</v>
+      </c>
+      <c r="C2220" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2220" s="20">
+        <v>162250</v>
+      </c>
+      <c r="E2220" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2220" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2220" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2221" s="2" t="s">
+        <v>4539</v>
+      </c>
+      <c r="B2221" s="2" t="s">
+        <v>4540</v>
+      </c>
+      <c r="C2221" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2221" s="20">
+        <v>162250</v>
+      </c>
+      <c r="E2221" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2221" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2221" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2222" s="2" t="s">
+        <v>4541</v>
+      </c>
+      <c r="B2222" s="2" t="s">
+        <v>4542</v>
+      </c>
+      <c r="C2222" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2222" s="20">
+        <v>148090</v>
+      </c>
+      <c r="E2222" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2222" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2222" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2223" s="2" t="s">
+        <v>4543</v>
+      </c>
+      <c r="B2223" s="2" t="s">
+        <v>4544</v>
+      </c>
+      <c r="C2223" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2223" s="20">
+        <v>66240</v>
+      </c>
+      <c r="E2223" s="2" t="s">
+        <v>3800</v>
+      </c>
+      <c r="F2223" s="2" t="s">
+        <v>4224</v>
+      </c>
+      <c r="G2223" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2224" s="2" t="s">
+        <v>4545</v>
+      </c>
+      <c r="B2224" s="2" t="s">
+        <v>4546</v>
+      </c>
+      <c r="C2224" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2224" s="20">
+        <v>54510</v>
+      </c>
+      <c r="E2224" s="2" t="s">
+        <v>3800</v>
+      </c>
+      <c r="F2224" s="2" t="s">
+        <v>4224</v>
+      </c>
+      <c r="G2224" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -65752,7 +67626,7 @@
     <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A952:A1795 A2:A950">
-    <cfRule type="duplicateValues" dxfId="4" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2009">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
